--- a/output/pdf_financials_xlsx/GLD.xlsx
+++ b/output/pdf_financials_xlsx/GLD.xlsx
@@ -5670,43 +5670,43 @@
         <v>0.746951</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.746951</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.759097</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.836491</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.9016380000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.088155</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.088155</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.088155</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.174736</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.772064</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.763495</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.763495</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.801786</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.801786</v>
       </c>
     </row>
     <row r="93">
@@ -9014,7 +9014,11 @@
           <t>Share-based payment reserve (note 8)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10450,7 +10454,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GLD.xlsx
+++ b/output/pdf_financials_xlsx/GLD.xlsx
@@ -999,52 +999,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001231</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003367</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000134</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000132</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000129</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000114</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000178</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-8e-06</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>9.1e-05</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.00013</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.002714</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.002523</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.002595</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>9.2e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1894,52 +1894,52 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.231433</v>
+        <v>-0.232664</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.086734</v>
+        <v>-2.090101</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.384592</v>
+        <v>-0.384726</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.6113499999999999</v>
+        <v>-0.611482</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.16336</v>
+        <v>-1.163489</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.759923</v>
+        <v>-1.760037</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.557975</v>
+        <v>-0.558153</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.811899</v>
+        <v>-0.811891</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.083897</v>
+        <v>-0.083967</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.227619</v>
+        <v>-0.227709</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.34692</v>
+        <v>-0.347011</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.760621</v>
+        <v>-0.760751</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.536428</v>
+        <v>-0.539142</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.141906</v>
+        <v>-1.144429</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-4.745599</v>
+        <v>-4.748194</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.022325</v>
+        <v>-1.022417</v>
       </c>
     </row>
     <row r="28">
@@ -2004,52 +2004,52 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.231433</v>
+        <v>-0.232664</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.086734</v>
+        <v>-2.090101</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.382036</v>
+        <v>-0.38217</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.609102</v>
+        <v>-0.6092340000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.161564</v>
+        <v>-1.161693</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.758483</v>
+        <v>-1.758597</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.556823</v>
+        <v>-0.557001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.810979</v>
+        <v>-0.810971</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.083161</v>
+        <v>-0.083231</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.227315</v>
+        <v>-0.227405</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.34668</v>
+        <v>-0.346771</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.760185</v>
+        <v>-0.760315</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.536192</v>
+        <v>-0.538906</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.141718</v>
+        <v>-1.144241</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.745447</v>
+        <v>-4.748042</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.022205</v>
+        <v>-1.022297</v>
       </c>
     </row>
     <row r="30">
@@ -2301,31 +2301,31 @@
         <v>0.394906</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.570014</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.6912</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.218406</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.042103</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.056863</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.04923</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.108208</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.031244</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.752301</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.941578</v>
@@ -2340,7 +2340,7 @@
         <v>0.076102</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.244397</v>
       </c>
     </row>
     <row r="35">
@@ -2411,31 +2411,31 @@
         <v>0.453392</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.260126</v>
+        <v>0.83014</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.072046</v>
+        <v>0.763246</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.011155</v>
+        <v>0.229561</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.3</v>
+        <v>0.342103</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.16</v>
+        <v>0.216863</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.048792</v>
+        <v>0.098022</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.202</v>
+        <v>0.310208</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.031244</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.752301</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.941578</v>
@@ -2450,7 +2450,7 @@
         <v>0.116102</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.245897</v>
       </c>
     </row>
     <row r="37">
@@ -3071,31 +3071,31 @@
         <v>0.02464</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.575914</v>
+        <v>0.0059</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.7022</v>
+        <v>0.011</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.26091</v>
+        <v>0.042504</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.054646</v>
+        <v>0.012543</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.099132</v>
+        <v>0.042269</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.055264</v>
+        <v>0.006034</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.114258</v>
+        <v>0.00605</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.037329</v>
+        <v>0.006085</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.759767</v>
+        <v>0.007466</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.007532</v>
@@ -3110,7 +3110,7 @@
         <v>0.00912</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.270184</v>
+        <v>0.025787</v>
       </c>
     </row>
     <row r="49">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8622,7 +8622,11 @@
           <t>Reclamation deposits (note 6)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -9970,7 +9974,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10066,7 +10070,11 @@
           <t>Reclamation deposits (note 5)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11198,7 +11206,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -22618,7 +22626,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
@@ -24088,7 +24096,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -25984,7 +25992,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">

--- a/output/pdf_financials_xlsx/GLD.xlsx
+++ b/output/pdf_financials_xlsx/GLD.xlsx
@@ -1277,10 +1277,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.026</v>
+        <v>-0.026</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.22607</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2152,7 +2152,7 @@
         <v>-1.245966184477753</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-58.78177393185505</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -6684,13 +6684,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002139</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002429</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001355</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001206</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.361959</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.073212</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.17679</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.025415</v>
       </c>
     </row>
     <row r="116">
@@ -7995,13 +7995,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002139</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002429</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001355</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001206</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -8050,13 +8050,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.224213</v>
+        <v>-0.226352</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.630707</v>
+        <v>-0.633136</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.507217</v>
+        <v>-0.508572</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.426101</v>
@@ -13408,7 +13408,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15344,7 +15348,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>-0.002139</v>
       </c>
@@ -15980,7 +15988,11 @@
           <t>Proceeds from sale of marketable securities, net</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -20336,7 +20348,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -32706,7 +32722,11 @@
           <t>Future income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
